--- a/5. Knife/output/yearly_benthic_cover_growth_param_0.5.xlsx
+++ b/5. Knife/output/yearly_benthic_cover_growth_param_0.5.xlsx
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>91.45465542203117</v>
+        <v>91.07584071383552</v>
       </c>
       <c r="C3" t="n">
-        <v>66.65219323412867</v>
+        <v>66.4544787921788</v>
       </c>
       <c r="D3" t="n">
-        <v>1.304879886913289</v>
+        <v>1.304816249228395</v>
       </c>
       <c r="E3" t="n">
-        <v>6.060819446243102</v>
+        <v>5.918453263357777</v>
       </c>
       <c r="F3" t="n">
-        <v>16.76268777803994</v>
+        <v>16.76187027854939</v>
       </c>
       <c r="G3" t="n">
-        <v>42.77400240409021</v>
+        <v>42.71554002581728</v>
       </c>
       <c r="H3" t="n">
-        <v>13.2495496209657</v>
+        <v>13.24890345370371</v>
       </c>
       <c r="I3" t="n">
-        <v>10.29896252661484</v>
+        <v>10.12255263608019</v>
       </c>
       <c r="J3" t="n">
-        <v>1.003753759164068</v>
+        <v>1.003704807098766</v>
       </c>
       <c r="K3" t="n">
-        <v>8.545344577968844</v>
+        <v>8.924159286164494</v>
       </c>
       <c r="L3" t="n">
-        <v>24.4604472786153</v>
+        <v>24.28518895644197</v>
       </c>
       <c r="M3" t="n">
-        <v>99.65798509071283</v>
+        <v>99.66382703478527</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>90.75646248291166</v>
+        <v>89.93916276235211</v>
       </c>
       <c r="C4" t="n">
-        <v>67.63460803819684</v>
+        <v>66.96991195381392</v>
       </c>
       <c r="D4" t="n">
-        <v>1.290690884645076</v>
+        <v>1.27911575926514</v>
       </c>
       <c r="E4" t="n">
-        <v>7.43320831603879</v>
+        <v>7.212198898289603</v>
       </c>
       <c r="F4" t="n">
-        <v>16.81569416683072</v>
+        <v>16.814438231404</v>
       </c>
       <c r="G4" t="n">
-        <v>42.30888647792795</v>
+        <v>41.87418760676384</v>
       </c>
       <c r="H4" t="n">
-        <v>13.29144688635722</v>
+        <v>13.29045417093011</v>
       </c>
       <c r="I4" t="n">
-        <v>8.609607956690889</v>
+        <v>8.461915506992584</v>
       </c>
       <c r="J4" t="n">
-        <v>1.006927794421001</v>
+        <v>1.006852588706826</v>
       </c>
       <c r="K4" t="n">
-        <v>9.243537517088376</v>
+        <v>10.06083723764789</v>
       </c>
       <c r="L4" t="n">
-        <v>22.83577215230881</v>
+        <v>22.68806879086931</v>
       </c>
       <c r="M4" t="n">
-        <v>99.71391770759402</v>
+        <v>99.71881798233112</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>89.5213256961987</v>
+        <v>88.25584624213911</v>
       </c>
       <c r="C5" t="n">
-        <v>67.80912194160337</v>
+        <v>66.67189001814744</v>
       </c>
       <c r="D5" t="n">
-        <v>1.261814138789278</v>
+        <v>1.239666758820951</v>
       </c>
       <c r="E5" t="n">
-        <v>8.505901363929899</v>
+        <v>8.16817315496424</v>
       </c>
       <c r="F5" t="n">
-        <v>16.86073754336079</v>
+        <v>16.85933998154356</v>
       </c>
       <c r="G5" t="n">
-        <v>41.36230586997635</v>
+        <v>40.5827526185433</v>
       </c>
       <c r="H5" t="n">
-        <v>13.3270500342732</v>
+        <v>13.32594537463323</v>
       </c>
       <c r="I5" t="n">
-        <v>7.193891743272748</v>
+        <v>7.070427037373739</v>
       </c>
       <c r="J5" t="n">
-        <v>1.009625002596455</v>
+        <v>1.009541316260093</v>
       </c>
       <c r="K5" t="n">
-        <v>10.47867430380129</v>
+        <v>11.7441537578609</v>
       </c>
       <c r="L5" t="n">
-        <v>21.47304797802062</v>
+        <v>21.34890301546409</v>
       </c>
       <c r="M5" t="n">
-        <v>99.76084422342527</v>
+        <v>99.76494679147243</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>87.7172955673059</v>
+        <v>85.84025502294951</v>
       </c>
       <c r="C6" t="n">
-        <v>67.18588041817361</v>
+        <v>65.41634504987323</v>
       </c>
       <c r="D6" t="n">
-        <v>1.220072783430555</v>
+        <v>1.182470393703484</v>
       </c>
       <c r="E6" t="n">
-        <v>9.225955495390007</v>
+        <v>8.7755616076113</v>
       </c>
       <c r="F6" t="n">
-        <v>16.89923599248765</v>
+        <v>16.89800226574985</v>
       </c>
       <c r="G6" t="n">
-        <v>39.99402297101353</v>
+        <v>38.71032527488384</v>
       </c>
       <c r="H6" t="n">
-        <v>13.3574799461579</v>
+        <v>13.35650478490407</v>
       </c>
       <c r="I6" t="n">
-        <v>6.00859807987489</v>
+        <v>5.905534272998162</v>
       </c>
       <c r="J6" t="n">
-        <v>1.011930298951356</v>
+        <v>1.011856423098793</v>
       </c>
       <c r="K6" t="n">
-        <v>12.2827044326941</v>
+        <v>14.15974497705051</v>
       </c>
       <c r="L6" t="n">
-        <v>20.33158482293028</v>
+        <v>20.2275092220381</v>
       </c>
       <c r="M6" t="n">
-        <v>99.800169673798</v>
+        <v>99.80359924896185</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85.21964105040863</v>
+        <v>82.67758179594595</v>
       </c>
       <c r="C7" t="n">
-        <v>65.6761602365182</v>
+        <v>63.22389940841691</v>
       </c>
       <c r="D7" t="n">
-        <v>1.161933774654182</v>
+        <v>1.107826592238132</v>
       </c>
       <c r="E7" t="n">
-        <v>9.622484672554359</v>
+        <v>9.043445359084714</v>
       </c>
       <c r="F7" t="n">
-        <v>16.93239865859427</v>
+        <v>16.93159666213639</v>
       </c>
       <c r="G7" t="n">
-        <v>38.08822449399459</v>
+        <v>36.26672427661462</v>
       </c>
       <c r="H7" t="n">
-        <v>13.38369235290086</v>
+        <v>13.38305843953295</v>
       </c>
       <c r="I7" t="n">
-        <v>5.016991010369393</v>
+        <v>4.931062402738148</v>
       </c>
       <c r="J7" t="n">
-        <v>1.013916087340974</v>
+        <v>1.013868063600981</v>
       </c>
       <c r="K7" t="n">
-        <v>14.78035894959137</v>
+        <v>17.32241820405405</v>
       </c>
       <c r="L7" t="n">
-        <v>19.37657531167167</v>
+        <v>19.28963976883466</v>
       </c>
       <c r="M7" t="n">
-        <v>99.83309449778125</v>
+        <v>99.83595738130562</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>81.72487447769311</v>
+        <v>78.44662749796504</v>
       </c>
       <c r="C8" t="n">
-        <v>63.00707933407761</v>
+        <v>59.80350837025101</v>
       </c>
       <c r="D8" t="n">
-        <v>1.080689490641371</v>
+        <v>1.008610410367003</v>
       </c>
       <c r="E8" t="n">
-        <v>9.647659578891037</v>
+        <v>8.919588365987263</v>
       </c>
       <c r="F8" t="n">
-        <v>16.96132185289704</v>
+        <v>16.96121226717439</v>
       </c>
       <c r="G8" t="n">
-        <v>35.4250343915683</v>
+        <v>33.01870158343375</v>
       </c>
       <c r="H8" t="n">
-        <v>13.40655379989467</v>
+        <v>13.40646718123964</v>
       </c>
       <c r="I8" t="n">
-        <v>4.187967348657135</v>
+        <v>4.116406236638778</v>
       </c>
       <c r="J8" t="n">
-        <v>1.015648015143536</v>
+        <v>1.015641453124215</v>
       </c>
       <c r="K8" t="n">
-        <v>18.27512552230691</v>
+        <v>21.55337250203498</v>
       </c>
       <c r="L8" t="n">
-        <v>18.57843428221633</v>
+        <v>18.50614517208239</v>
       </c>
       <c r="M8" t="n">
-        <v>99.86063913860085</v>
+        <v>99.86302604436837</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>77.34103718401163</v>
+        <v>73.33091132198473</v>
       </c>
       <c r="C9" t="n">
-        <v>59.31253015207423</v>
+        <v>55.36411953940416</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9795145144891095</v>
+        <v>0.889855071199301</v>
       </c>
       <c r="E9" t="n">
-        <v>9.326976670919779</v>
+        <v>8.441998295665798</v>
       </c>
       <c r="F9" t="n">
-        <v>16.9868726365675</v>
+        <v>16.9877011264511</v>
       </c>
       <c r="G9" t="n">
-        <v>32.10851559426526</v>
+        <v>29.13102893489245</v>
       </c>
       <c r="H9" t="n">
-        <v>13.42674962890365</v>
+        <v>13.4274044831829</v>
       </c>
       <c r="I9" t="n">
-        <v>3.495230136676671</v>
+        <v>3.43569579823084</v>
       </c>
       <c r="J9" t="n">
-        <v>1.017178002189671</v>
+        <v>1.017227612362341</v>
       </c>
       <c r="K9" t="n">
-        <v>22.65896281598836</v>
+        <v>26.66908867801527</v>
       </c>
       <c r="L9" t="n">
-        <v>17.91217460558582</v>
+        <v>17.85244716489617</v>
       </c>
       <c r="M9" t="n">
-        <v>99.88366757364841</v>
+        <v>99.8856553823156</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>72.23777517265813</v>
+        <v>67.66035513230702</v>
       </c>
       <c r="C10" t="n">
-        <v>54.7840660349821</v>
+        <v>50.25720721050745</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8628215633859032</v>
+        <v>0.7597359717829218</v>
       </c>
       <c r="E10" t="n">
-        <v>8.701923654682899</v>
+        <v>7.685420692482298</v>
       </c>
       <c r="F10" t="n">
-        <v>17.00973422708317</v>
+        <v>17.01169639160022</v>
       </c>
       <c r="G10" t="n">
-        <v>28.2833171058157</v>
+        <v>24.87134286604525</v>
       </c>
       <c r="H10" t="n">
-        <v>13.44481986811364</v>
+        <v>13.44637080054628</v>
       </c>
       <c r="I10" t="n">
-        <v>2.916611793871243</v>
+        <v>2.867123955263204</v>
       </c>
       <c r="J10" t="n">
-        <v>1.018546959705579</v>
+        <v>1.018664454586839</v>
       </c>
       <c r="K10" t="n">
-        <v>27.76222482734187</v>
+        <v>32.33964486769298</v>
       </c>
       <c r="L10" t="n">
-        <v>17.35661941165722</v>
+        <v>17.30771192740428</v>
       </c>
       <c r="M10" t="n">
-        <v>99.90291027398121</v>
+        <v>99.9045640056047</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>66.74298235937395</v>
+        <v>61.90986301305585</v>
       </c>
       <c r="C11" t="n">
-        <v>49.7680887090545</v>
+        <v>44.97591546311273</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7377137912422026</v>
+        <v>0.6294137697385319</v>
       </c>
       <c r="E11" t="n">
-        <v>7.878172721981595</v>
+        <v>6.765817618669635</v>
       </c>
       <c r="F11" t="n">
-        <v>17.03040684801376</v>
+        <v>17.03360883439152</v>
       </c>
       <c r="G11" t="n">
-        <v>24.18228052757268</v>
+        <v>20.60500786219187</v>
       </c>
       <c r="H11" t="n">
-        <v>13.46115990381926</v>
+        <v>13.46369081520767</v>
       </c>
       <c r="I11" t="n">
-        <v>2.433463725546019</v>
+        <v>2.392347535946949</v>
       </c>
       <c r="J11" t="n">
-        <v>1.019784841198429</v>
+        <v>1.019976576909672</v>
       </c>
       <c r="K11" t="n">
-        <v>33.25701764062605</v>
+        <v>38.09013698694416</v>
       </c>
       <c r="L11" t="n">
-        <v>16.89387665604526</v>
+        <v>16.85430521785246</v>
       </c>
       <c r="M11" t="n">
-        <v>99.91898300572581</v>
+        <v>99.92035766790934</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>61.27478509139779</v>
+        <v>56.36814838205538</v>
       </c>
       <c r="C12" t="n">
-        <v>44.69835769382659</v>
+        <v>39.82440394509484</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6132746582803035</v>
+        <v>0.5054381568858772</v>
       </c>
       <c r="E12" t="n">
-        <v>6.982070256182965</v>
+        <v>5.765817386163008</v>
       </c>
       <c r="F12" t="n">
-        <v>17.04921494976003</v>
+        <v>17.05371396850752</v>
       </c>
       <c r="G12" t="n">
-        <v>20.10316196205763</v>
+        <v>16.5464400323044</v>
       </c>
       <c r="H12" t="n">
-        <v>13.47602618783428</v>
+        <v>13.47958229846103</v>
       </c>
       <c r="I12" t="n">
-        <v>2.030126002446652</v>
+        <v>1.995976062577407</v>
       </c>
       <c r="J12" t="n">
-        <v>1.02091107483593</v>
+        <v>1.021180477156138</v>
       </c>
       <c r="K12" t="n">
-        <v>38.7252149086022</v>
+        <v>43.63185161794462</v>
       </c>
       <c r="L12" t="n">
-        <v>16.50883118297271</v>
+        <v>16.4772903387398</v>
       </c>
       <c r="M12" t="n">
-        <v>99.9324037854015</v>
+        <v>99.93354590177925</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>56.18330405249525</v>
+        <v>51.32944218048779</v>
       </c>
       <c r="C13" t="n">
-        <v>39.93820273216264</v>
+        <v>35.10992223987341</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5003765464460739</v>
+        <v>0.3942508812026644</v>
       </c>
       <c r="E13" t="n">
-        <v>6.009250067095689</v>
+        <v>4.774960245739222</v>
       </c>
       <c r="F13" t="n">
-        <v>17.06634480658557</v>
+        <v>17.07215455021924</v>
       </c>
       <c r="G13" t="n">
-        <v>16.4023584203325</v>
+        <v>12.90652174678609</v>
       </c>
       <c r="H13" t="n">
-        <v>13.48956595490596</v>
+        <v>13.49415808759844</v>
       </c>
       <c r="I13" t="n">
-        <v>1.693471442363851</v>
+        <v>1.6651119653362</v>
       </c>
       <c r="J13" t="n">
-        <v>1.021936814765603</v>
+        <v>1.022284703605942</v>
       </c>
       <c r="K13" t="n">
-        <v>43.81669594750475</v>
+        <v>48.67055781951221</v>
       </c>
       <c r="L13" t="n">
-        <v>16.18870893137575</v>
+        <v>16.16407616109834</v>
       </c>
       <c r="M13" t="n">
-        <v>99.94360761104313</v>
+        <v>99.94455622048396</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>51.96454763528289</v>
+        <v>47.40398775696248</v>
       </c>
       <c r="C14" t="n">
-        <v>35.99477779024247</v>
+        <v>31.45369855116305</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4058707775929917</v>
+        <v>0.30893399575074</v>
       </c>
       <c r="E14" t="n">
-        <v>5.235256242074909</v>
+        <v>3.973138222549849</v>
       </c>
       <c r="F14" t="n">
-        <v>17.08180810240816</v>
+        <v>17.08882849484027</v>
       </c>
       <c r="G14" t="n">
-        <v>13.30445644125882</v>
+        <v>10.11351787550932</v>
       </c>
       <c r="H14" t="n">
-        <v>13.50178844022681</v>
+        <v>13.50733749292764</v>
       </c>
       <c r="I14" t="n">
-        <v>1.412504871097973</v>
+        <v>1.388948531981051</v>
       </c>
       <c r="J14" t="n">
-        <v>1.022862760623243</v>
+        <v>1.023283143403608</v>
       </c>
       <c r="K14" t="n">
-        <v>48.0354523647171</v>
+        <v>52.59601224303752</v>
       </c>
       <c r="L14" t="n">
-        <v>15.92272897164144</v>
+        <v>15.90403609565121</v>
       </c>
       <c r="M14" t="n">
-        <v>99.952959126601</v>
+        <v>99.95374688985177</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>48.63165162404357</v>
+        <v>44.21759135582055</v>
       </c>
       <c r="C15" t="n">
-        <v>32.89067678419249</v>
+        <v>28.49093170583896</v>
       </c>
       <c r="D15" t="n">
-        <v>0.332589726596959</v>
+        <v>0.2407414284077772</v>
       </c>
       <c r="E15" t="n">
-        <v>4.58674256454235</v>
+        <v>3.290209542140749</v>
       </c>
       <c r="F15" t="n">
-        <v>17.09560091403907</v>
+        <v>17.10375231370654</v>
       </c>
       <c r="G15" t="n">
-        <v>10.90230135946557</v>
+        <v>7.881109793893147</v>
       </c>
       <c r="H15" t="n">
-        <v>13.51269054283328</v>
+        <v>13.51913356532493</v>
       </c>
       <c r="I15" t="n">
-        <v>1.178037839078975</v>
+        <v>1.158467927095522</v>
       </c>
       <c r="J15" t="n">
-        <v>1.023688677487369</v>
+        <v>1.024176785251888</v>
       </c>
       <c r="K15" t="n">
-        <v>51.36834837595643</v>
+        <v>55.78240864417944</v>
       </c>
       <c r="L15" t="n">
-        <v>15.70173859343169</v>
+        <v>15.68807774631546</v>
       </c>
       <c r="M15" t="n">
-        <v>99.96076375358061</v>
+        <v>99.96141809633386</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>67.48814850185134</v>
+        <v>63.53968686257224</v>
       </c>
       <c r="C16" t="n">
-        <v>36.49572560280359</v>
+        <v>32.50431016720439</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3351453457501016</v>
+        <v>0.2426843464075465</v>
       </c>
       <c r="E16" t="n">
-        <v>7.721428347664545</v>
+        <v>6.609108663460933</v>
       </c>
       <c r="F16" t="n">
-        <v>17.22696349573224</v>
+        <v>17.24178916284249</v>
       </c>
       <c r="G16" t="n">
-        <v>11.49262153560755</v>
+        <v>8.67305596069197</v>
       </c>
       <c r="H16" t="n">
-        <v>14.12306894705834</v>
+        <v>14.35658173791101</v>
       </c>
       <c r="I16" t="n">
-        <v>15.55736612969532</v>
+        <v>15.38402452641742</v>
       </c>
       <c r="J16" t="n">
-        <v>1.031554700343248</v>
+        <v>1.032442464840867</v>
       </c>
       <c r="K16" t="n">
-        <v>32.51185149814865</v>
+        <v>36.46031313742777</v>
       </c>
       <c r="L16" t="n">
-        <v>30.47779840221803</v>
+        <v>30.52668133395511</v>
       </c>
       <c r="M16" t="n">
-        <v>99.48537550317027</v>
+        <v>99.49130463858728</v>
       </c>
     </row>
   </sheetData>
